--- a/运气工程/运气工程-04-SlotsRTP计算规则-免费篇.xlsx
+++ b/运气工程/运气工程-04-SlotsRTP计算规则-免费篇.xlsx
@@ -7742,6 +7742,9 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:F89" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -9995,6 +9998,9 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M102" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -11336,6 +11342,9 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:V43" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -12968,6 +12977,9 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M78" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -13574,6 +13586,9 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:J53" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -14161,5 +14176,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:K46" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/运气工程/运气工程-04-SlotsRTP计算规则-免费篇.xlsx
+++ b/运气工程/运气工程-04-SlotsRTP计算规则-免费篇.xlsx
@@ -14,7 +14,7 @@
     <sheet name="免费游戏RTP" sheetId="5" r:id="rId5"/>
     <sheet name="再触发与波动" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="212">
   <si>
     <r>
       <rPr>
@@ -6809,7 +6809,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -6864,6 +6864,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -7509,28 +7517,28 @@
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="34" t="s">
-        <v>20</v>
+      <c r="A24" s="37">
+        <v>3.1</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="34" t="s">
-        <v>21</v>
+      <c r="A25" s="37">
+        <v>3.2</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="34" t="s">
-        <v>22</v>
+      <c r="A26" s="37">
+        <v>3.3</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="34" t="s">
-        <v>23</v>
+      <c r="A27" s="37">
+        <v>3.4</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="34" t="s">
-        <v>24</v>
+      <c r="A28" s="37">
+        <v>3.5</v>
       </c>
     </row>
     <row r="29" spans="1:1">
@@ -7539,18 +7547,18 @@
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="34" t="s">
-        <v>26</v>
+      <c r="A30" s="37">
+        <v>4.1</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="34" t="s">
-        <v>27</v>
+      <c r="A31" s="37">
+        <v>4.2</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="34" t="s">
-        <v>28</v>
+      <c r="A32" s="37">
+        <v>4.3</v>
       </c>
     </row>
     <row r="33" spans="1:1">
@@ -7619,8 +7627,8 @@
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="34" t="s">
-        <v>40</v>
+      <c r="A46" s="37">
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -8076,8 +8084,8 @@
       <c r="A13">
         <v>9</v>
       </c>
-      <c r="B13" s="32" t="s">
-        <v>73</v>
+      <c r="B13" s="38">
+        <v>10</v>
       </c>
       <c r="C13" s="32" t="s">
         <v>72</v>
@@ -8102,8 +8110,8 @@
       <c r="A14">
         <v>10</v>
       </c>
-      <c r="B14" s="32" t="s">
-        <v>73</v>
+      <c r="B14" s="38">
+        <v>10</v>
       </c>
       <c r="C14" s="32" t="s">
         <v>72</v>
@@ -8128,8 +8136,8 @@
       <c r="A15">
         <v>11</v>
       </c>
-      <c r="B15" s="32" t="s">
-        <v>73</v>
+      <c r="B15" s="38">
+        <v>10</v>
       </c>
       <c r="C15" s="32" t="s">
         <v>72</v>
@@ -8154,20 +8162,20 @@
       <c r="A16">
         <v>12</v>
       </c>
-      <c r="B16" s="32" t="s">
-        <v>73</v>
+      <c r="B16" s="38">
+        <v>10</v>
       </c>
       <c r="C16" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="F16" s="32" t="s">
-        <v>73</v>
+      <c r="D16" s="38">
+        <v>10</v>
+      </c>
+      <c r="E16" s="38">
+        <v>10</v>
+      </c>
+      <c r="F16" s="38">
+        <v>10</v>
       </c>
       <c r="G16" s="18" t="s">
         <v>1</v>
@@ -8180,20 +8188,20 @@
       <c r="A17">
         <v>13</v>
       </c>
-      <c r="B17" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="E17" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17" s="32" t="s">
-        <v>73</v>
+      <c r="B17" s="38">
+        <v>10</v>
+      </c>
+      <c r="C17" s="38">
+        <v>10</v>
+      </c>
+      <c r="D17" s="38">
+        <v>10</v>
+      </c>
+      <c r="E17" s="38">
+        <v>10</v>
+      </c>
+      <c r="F17" s="38">
+        <v>10</v>
       </c>
       <c r="G17" s="18" t="s">
         <v>1</v>
@@ -8206,20 +8214,20 @@
       <c r="A18">
         <v>14</v>
       </c>
-      <c r="B18" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" s="32" t="s">
-        <v>73</v>
+      <c r="B18" s="38">
+        <v>9</v>
+      </c>
+      <c r="C18" s="38">
+        <v>10</v>
+      </c>
+      <c r="D18" s="38">
+        <v>10</v>
+      </c>
+      <c r="E18" s="38">
+        <v>10</v>
+      </c>
+      <c r="F18" s="38">
+        <v>10</v>
       </c>
       <c r="G18" s="18" t="s">
         <v>1</v>
@@ -8232,20 +8240,20 @@
       <c r="A19">
         <v>15</v>
       </c>
-      <c r="B19" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="F19" s="32" t="s">
-        <v>73</v>
+      <c r="B19" s="38">
+        <v>9</v>
+      </c>
+      <c r="C19" s="38">
+        <v>10</v>
+      </c>
+      <c r="D19" s="38">
+        <v>10</v>
+      </c>
+      <c r="E19" s="38">
+        <v>10</v>
+      </c>
+      <c r="F19" s="38">
+        <v>10</v>
       </c>
       <c r="G19" s="18" t="s">
         <v>1</v>
@@ -8258,20 +8266,20 @@
       <c r="A20">
         <v>16</v>
       </c>
-      <c r="B20" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="F20" s="32" t="s">
-        <v>74</v>
+      <c r="B20" s="38">
+        <v>9</v>
+      </c>
+      <c r="C20" s="38">
+        <v>9</v>
+      </c>
+      <c r="D20" s="38">
+        <v>9</v>
+      </c>
+      <c r="E20" s="38">
+        <v>9</v>
+      </c>
+      <c r="F20" s="38">
+        <v>9</v>
       </c>
       <c r="G20" s="18" t="s">
         <v>1</v>
@@ -8284,20 +8292,20 @@
       <c r="A21">
         <v>17</v>
       </c>
-      <c r="B21" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="F21" s="32" t="s">
-        <v>74</v>
+      <c r="B21" s="38">
+        <v>9</v>
+      </c>
+      <c r="C21" s="38">
+        <v>9</v>
+      </c>
+      <c r="D21" s="38">
+        <v>9</v>
+      </c>
+      <c r="E21" s="38">
+        <v>9</v>
+      </c>
+      <c r="F21" s="38">
+        <v>9</v>
       </c>
       <c r="G21" s="18" t="s">
         <v>1</v>
@@ -8310,20 +8318,20 @@
       <c r="A22">
         <v>18</v>
       </c>
-      <c r="B22" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="D22" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="F22" s="32" t="s">
-        <v>74</v>
+      <c r="B22" s="38">
+        <v>9</v>
+      </c>
+      <c r="C22" s="38">
+        <v>9</v>
+      </c>
+      <c r="D22" s="38">
+        <v>9</v>
+      </c>
+      <c r="E22" s="38">
+        <v>9</v>
+      </c>
+      <c r="F22" s="38">
+        <v>9</v>
       </c>
       <c r="G22" s="18" t="s">
         <v>1</v>
@@ -8336,20 +8344,20 @@
       <c r="A23">
         <v>19</v>
       </c>
-      <c r="B23" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="E23" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" s="32" t="s">
-        <v>74</v>
+      <c r="B23" s="38">
+        <v>9</v>
+      </c>
+      <c r="C23" s="38">
+        <v>9</v>
+      </c>
+      <c r="D23" s="38">
+        <v>9</v>
+      </c>
+      <c r="E23" s="38">
+        <v>9</v>
+      </c>
+      <c r="F23" s="38">
+        <v>9</v>
       </c>
       <c r="G23" s="18" t="s">
         <v>1</v>
@@ -8650,8 +8658,8 @@
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="5" t="s">
-        <v>73</v>
+      <c r="A34" s="39">
+        <v>10</v>
       </c>
       <c r="B34" s="10">
         <f t="shared" si="0"/>
@@ -8681,8 +8689,8 @@
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="5" t="s">
-        <v>74</v>
+      <c r="A35" s="39">
+        <v>9</v>
       </c>
       <c r="B35" s="10">
         <f t="shared" si="0"/>
@@ -9063,8 +9071,8 @@
       <c r="A49">
         <v>9</v>
       </c>
-      <c r="B49" s="32" t="s">
-        <v>73</v>
+      <c r="B49" s="38">
+        <v>10</v>
       </c>
       <c r="C49" s="32" t="s">
         <v>72</v>
@@ -9089,8 +9097,8 @@
       <c r="A50">
         <v>10</v>
       </c>
-      <c r="B50" s="32" t="s">
-        <v>73</v>
+      <c r="B50" s="38">
+        <v>10</v>
       </c>
       <c r="C50" s="32" t="s">
         <v>72</v>
@@ -9115,8 +9123,8 @@
       <c r="A51">
         <v>11</v>
       </c>
-      <c r="B51" s="32" t="s">
-        <v>73</v>
+      <c r="B51" s="38">
+        <v>10</v>
       </c>
       <c r="C51" s="32" t="s">
         <v>72</v>
@@ -9141,20 +9149,20 @@
       <c r="A52">
         <v>12</v>
       </c>
-      <c r="B52" s="32" t="s">
-        <v>73</v>
+      <c r="B52" s="38">
+        <v>10</v>
       </c>
       <c r="C52" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="D52" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="E52" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="F52" s="32" t="s">
-        <v>73</v>
+      <c r="D52" s="38">
+        <v>10</v>
+      </c>
+      <c r="E52" s="38">
+        <v>10</v>
+      </c>
+      <c r="F52" s="38">
+        <v>10</v>
       </c>
       <c r="G52" s="18" t="s">
         <v>1</v>
@@ -9167,20 +9175,20 @@
       <c r="A53">
         <v>13</v>
       </c>
-      <c r="B53" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="C53" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="D53" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="E53" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="F53" s="32" t="s">
-        <v>73</v>
+      <c r="B53" s="38">
+        <v>10</v>
+      </c>
+      <c r="C53" s="38">
+        <v>10</v>
+      </c>
+      <c r="D53" s="38">
+        <v>10</v>
+      </c>
+      <c r="E53" s="38">
+        <v>10</v>
+      </c>
+      <c r="F53" s="38">
+        <v>10</v>
       </c>
       <c r="G53" s="18" t="s">
         <v>1</v>
@@ -9193,20 +9201,20 @@
       <c r="A54">
         <v>14</v>
       </c>
-      <c r="B54" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C54" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="D54" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="E54" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="F54" s="32" t="s">
-        <v>73</v>
+      <c r="B54" s="38">
+        <v>9</v>
+      </c>
+      <c r="C54" s="38">
+        <v>10</v>
+      </c>
+      <c r="D54" s="38">
+        <v>10</v>
+      </c>
+      <c r="E54" s="38">
+        <v>10</v>
+      </c>
+      <c r="F54" s="38">
+        <v>10</v>
       </c>
       <c r="G54" s="18" t="s">
         <v>1</v>
@@ -9219,20 +9227,20 @@
       <c r="A55">
         <v>15</v>
       </c>
-      <c r="B55" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C55" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="D55" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="E55" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="F55" s="32" t="s">
-        <v>73</v>
+      <c r="B55" s="38">
+        <v>9</v>
+      </c>
+      <c r="C55" s="38">
+        <v>10</v>
+      </c>
+      <c r="D55" s="38">
+        <v>10</v>
+      </c>
+      <c r="E55" s="38">
+        <v>10</v>
+      </c>
+      <c r="F55" s="38">
+        <v>10</v>
       </c>
       <c r="G55" s="18" t="s">
         <v>1</v>
@@ -9245,20 +9253,20 @@
       <c r="A56">
         <v>16</v>
       </c>
-      <c r="B56" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C56" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="D56" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="E56" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="F56" s="32" t="s">
-        <v>74</v>
+      <c r="B56" s="38">
+        <v>9</v>
+      </c>
+      <c r="C56" s="38">
+        <v>9</v>
+      </c>
+      <c r="D56" s="38">
+        <v>9</v>
+      </c>
+      <c r="E56" s="38">
+        <v>9</v>
+      </c>
+      <c r="F56" s="38">
+        <v>9</v>
       </c>
       <c r="G56" s="18" t="s">
         <v>1</v>
@@ -9271,20 +9279,20 @@
       <c r="A57">
         <v>17</v>
       </c>
-      <c r="B57" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C57" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="D57" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="E57" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="F57" s="32" t="s">
-        <v>74</v>
+      <c r="B57" s="38">
+        <v>9</v>
+      </c>
+      <c r="C57" s="38">
+        <v>9</v>
+      </c>
+      <c r="D57" s="38">
+        <v>9</v>
+      </c>
+      <c r="E57" s="38">
+        <v>9</v>
+      </c>
+      <c r="F57" s="38">
+        <v>9</v>
       </c>
       <c r="G57" s="18" t="s">
         <v>1</v>
@@ -9297,20 +9305,20 @@
       <c r="A58">
         <v>18</v>
       </c>
-      <c r="B58" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C58" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="D58" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="E58" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="F58" s="32" t="s">
-        <v>74</v>
+      <c r="B58" s="38">
+        <v>9</v>
+      </c>
+      <c r="C58" s="38">
+        <v>9</v>
+      </c>
+      <c r="D58" s="38">
+        <v>9</v>
+      </c>
+      <c r="E58" s="38">
+        <v>9</v>
+      </c>
+      <c r="F58" s="38">
+        <v>9</v>
       </c>
       <c r="G58" s="18" t="s">
         <v>1</v>
@@ -9323,17 +9331,17 @@
       <c r="A59">
         <v>19</v>
       </c>
-      <c r="B59" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C59" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="D59" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="E59" s="32" t="s">
-        <v>74</v>
+      <c r="B59" s="38">
+        <v>9</v>
+      </c>
+      <c r="C59" s="38">
+        <v>9</v>
+      </c>
+      <c r="D59" s="38">
+        <v>9</v>
+      </c>
+      <c r="E59" s="38">
+        <v>9</v>
       </c>
       <c r="F59" s="32" t="s">
         <v>75</v>
@@ -9637,8 +9645,8 @@
       </c>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="5" t="s">
-        <v>73</v>
+      <c r="A70" s="39">
+        <v>10</v>
       </c>
       <c r="B70" s="10">
         <f t="shared" si="5"/>
@@ -9668,8 +9676,8 @@
       </c>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="5" t="s">
-        <v>74</v>
+      <c r="A71" s="39">
+        <v>9</v>
       </c>
       <c r="B71" s="10">
         <f t="shared" si="5"/>
@@ -9816,14 +9824,14 @@
       <c r="A76" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B76" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C76" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D76" s="13" t="s">
-        <v>86</v>
+      <c r="B76" s="40">
+        <v>3</v>
+      </c>
+      <c r="C76" s="40">
+        <v>4</v>
+      </c>
+      <c r="D76" s="40">
+        <v>5</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>1</v>
@@ -9917,8 +9925,8 @@
       </c>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="5" t="s">
-        <v>73</v>
+      <c r="A80" s="39">
+        <v>10</v>
       </c>
       <c r="B80" s="23">
         <v>5</v>
@@ -9943,8 +9951,8 @@
       </c>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="5" t="s">
-        <v>74</v>
+      <c r="A81" s="39">
+        <v>9</v>
       </c>
       <c r="B81" s="23">
         <v>5</v>
@@ -10189,14 +10197,14 @@
       <c r="I4" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="J4" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="L4" s="13" t="s">
-        <v>101</v>
+      <c r="J4" s="40">
+        <v>5</v>
+      </c>
+      <c r="K4" s="40">
+        <v>4</v>
+      </c>
+      <c r="L4" s="40">
+        <v>3</v>
       </c>
       <c r="M4" s="9" t="s">
         <v>102</v>
@@ -10419,8 +10427,8 @@
       </c>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="5" t="s">
-        <v>73</v>
+      <c r="A8" s="39">
+        <v>10</v>
       </c>
       <c r="B8" s="10">
         <f>滚轴与计数!B34+滚轴与计数!B$30</f>
@@ -10487,8 +10495,8 @@
       </c>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="5" t="s">
-        <v>74</v>
+      <c r="A9" s="39">
+        <v>9</v>
       </c>
       <c r="B9" s="10">
         <f>滚轴与计数!B35+滚轴与计数!B$30</f>
@@ -10833,14 +10841,14 @@
       <c r="I15" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="J15" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>101</v>
+      <c r="J15" s="40">
+        <v>5</v>
+      </c>
+      <c r="K15" s="40">
+        <v>4</v>
+      </c>
+      <c r="L15" s="40">
+        <v>3</v>
       </c>
       <c r="M15" s="9" t="s">
         <v>102</v>
@@ -11063,8 +11071,8 @@
       </c>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="5" t="s">
-        <v>73</v>
+      <c r="A19" s="39">
+        <v>10</v>
       </c>
       <c r="B19" s="10">
         <f>滚轴与计数!B70+滚轴与计数!B$66</f>
@@ -11131,8 +11139,8 @@
       </c>
     </row>
     <row r="20" spans="1:17">
-      <c r="A20" s="5" t="s">
-        <v>74</v>
+      <c r="A20" s="39">
+        <v>9</v>
       </c>
       <c r="B20" s="10">
         <f>滚轴与计数!B71+滚轴与计数!B$66</f>
@@ -13049,14 +13057,14 @@
       <c r="A4" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>156</v>
+      <c r="B4" s="40">
+        <v>3</v>
+      </c>
+      <c r="C4" s="40">
+        <v>4</v>
+      </c>
+      <c r="D4" s="40">
+        <v>5</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>157</v>
@@ -13271,14 +13279,14 @@
       <c r="A16" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B16" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>156</v>
+      <c r="B16" s="40">
+        <v>3</v>
+      </c>
+      <c r="C16" s="40">
+        <v>4</v>
+      </c>
+      <c r="D16" s="40">
+        <v>5</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>167</v>
@@ -13809,8 +13817,8 @@
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
-        <v>197</v>
+      <c r="A11" s="39">
+        <v>3</v>
       </c>
       <c r="B11" s="10">
         <f>免费游戏RTP!B7</f>
@@ -13833,8 +13841,8 @@
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
-        <v>198</v>
+      <c r="A12" s="39">
+        <v>4</v>
       </c>
       <c r="B12" s="10">
         <f>免费游戏RTP!C7</f>
@@ -13857,8 +13865,8 @@
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
-        <v>199</v>
+      <c r="A13" s="39">
+        <v>5</v>
       </c>
       <c r="B13" s="10">
         <f>免费游戏RTP!D7</f>
@@ -13876,8 +13884,8 @@
         <f>C13*D13</f>
         <v>28.6412391646785</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>200</v>
+      <c r="F13" s="39">
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6">

--- a/运气工程/运气工程-04-SlotsRTP计算规则-免费篇.xlsx
+++ b/运气工程/运气工程-04-SlotsRTP计算规则-免费篇.xlsx
@@ -6104,7 +6104,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -6112,6 +6112,7 @@
     <numFmt numFmtId="176" formatCode="0.00000000"/>
     <numFmt numFmtId="177" formatCode="0.0000%"/>
     <numFmt numFmtId="178" formatCode="0.0000"/>
+    <numFmt numFmtId="179" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="33">
     <font>
@@ -6809,7 +6810,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -6873,6 +6874,11 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="179" applyNumberFormat="1" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="179" applyNumberFormat="1" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="179" applyNumberFormat="1" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="179" applyNumberFormat="1" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="179" applyNumberFormat="1" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -10282,7 +10288,7 @@
         <f>VLOOKUP($A5,滚轴与计数!$A$77:$D$81,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P5" s="8">
+      <c r="P5" s="42">
         <f>(J5*M5+K5*N5+L5*O5)/滚轴与计数!$H$25</f>
         <v>0.0256</v>
       </c>
@@ -10350,7 +10356,7 @@
         <f>VLOOKUP($A6,滚轴与计数!$A$77:$D$81,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P6" s="8">
+      <c r="P6" s="42">
         <f>(J6*M6+K6*N6+L6*O6)/滚轴与计数!$H$25</f>
         <v>0.072</v>
       </c>
@@ -10418,7 +10424,7 @@
         <f>VLOOKUP($A7,滚轴与计数!$A$77:$D$81,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P7" s="8">
+      <c r="P7" s="42">
         <f>(J7*M7+K7*N7+L7*O7)/滚轴与计数!$H$25</f>
         <v>0.1828125</v>
       </c>
@@ -10486,7 +10492,7 @@
         <f>VLOOKUP($A8,滚轴与计数!$A$77:$D$81,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P8" s="8">
+      <c r="P8" s="42">
         <f>(J8*M8+K8*N8+L8*O8)/滚轴与计数!$H$25</f>
         <v>0.15234375</v>
       </c>
@@ -10554,7 +10560,7 @@
         <f>VLOOKUP($A9,滚轴与计数!$A$77:$D$81,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P9" s="8">
+      <c r="P9" s="42">
         <f>(J9*M9+K9*N9+L9*O9)/滚轴与计数!$H$25</f>
         <v>0.1640625</v>
       </c>
@@ -10611,7 +10617,7 @@
       <c r="O10" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="P10" s="16">
+      <c r="P10" s="43">
         <f>SUM(P5:P9)</f>
         <v>0.59681875</v>
       </c>
@@ -10655,7 +10661,7 @@
       <c r="O11" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="P11" s="8">
+      <c r="P11" s="42">
         <f>滚轴与计数!$B$82*Scatter与触发率!$D$21</f>
         <v>0.05322375</v>
       </c>
@@ -10699,7 +10705,7 @@
       <c r="O12" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="P12" s="16">
+      <c r="P12" s="43">
         <f>P10+P11</f>
         <v>0.6500425</v>
       </c>
@@ -10926,7 +10932,7 @@
         <f>VLOOKUP($A16,滚轴与计数!$A$77:$D$81,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P16" s="8">
+      <c r="P16" s="42">
         <f>(J16*M16+K16*N16+L16*O16)/滚轴与计数!$H$61</f>
         <v>0.0495476973684211</v>
       </c>
@@ -10994,7 +11000,7 @@
         <f>VLOOKUP($A17,滚轴与计数!$A$77:$D$81,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P17" s="8">
+      <c r="P17" s="42">
         <f>(J17*M17+K17*N17+L17*O17)/滚轴与计数!$H$61</f>
         <v>0.0729473684210526</v>
       </c>
@@ -11062,7 +11068,7 @@
         <f>VLOOKUP($A18,滚轴与计数!$A$77:$D$81,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P18" s="8">
+      <c r="P18" s="42">
         <f>(J18*M18+K18*N18+L18*O18)/滚轴与计数!$H$61</f>
         <v>0.308921052631579</v>
       </c>
@@ -11130,7 +11136,7 @@
         <f>VLOOKUP($A19,滚轴与计数!$A$77:$D$81,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P19" s="8">
+      <c r="P19" s="42">
         <f>(J19*M19+K19*N19+L19*O19)/滚轴与计数!$H$61</f>
         <v>0.275822368421053</v>
       </c>
@@ -11198,7 +11204,7 @@
         <f>VLOOKUP($A20,滚轴与计数!$A$77:$D$81,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P20" s="8">
+      <c r="P20" s="42">
         <f>(J20*M20+K20*N20+L20*O20)/滚轴与计数!$H$61</f>
         <v>0.260763157894737</v>
       </c>
@@ -11255,7 +11261,7 @@
       <c r="O21" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="P21" s="16">
+      <c r="P21" s="43">
         <f>SUM(P16:P20)</f>
         <v>0.968001644736842</v>
       </c>
@@ -11293,7 +11299,7 @@
       <c r="O22" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="P22" s="8">
+      <c r="P22" s="42">
         <f>Scatter与触发率!$C$58</f>
         <v>0.0547638157894737</v>
       </c>
@@ -11331,7 +11337,7 @@
       <c r="O23" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="P23" s="16">
+      <c r="P23" s="43">
         <f>P21+P22</f>
         <v>1.02276546052632</v>
       </c>
@@ -11755,23 +11761,23 @@
       <c r="A15" t="s">
         <v>128</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="42">
         <f>B13/B11</f>
         <v>0.15</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="42">
         <f>C13/C11</f>
         <v>0.15</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="42">
         <f>D13/D11</f>
         <v>0.15</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="42">
         <f>E13/E11</f>
         <v>0.15</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="42">
         <f>F13/F11</f>
         <v>0.15</v>
       </c>
@@ -11841,18 +11847,18 @@
       <c r="B18" s="23">
         <v>10</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="42">
         <f>$B$15^A18*(1-$B$15)^(5-A18)</f>
         <v>0.0024384375</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="43">
         <f>B18*C18</f>
         <v>0.024384375</v>
       </c>
       <c r="E18" s="23">
         <v>10</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="42">
         <f>D18*E18</f>
         <v>0.24384375</v>
       </c>
@@ -11870,18 +11876,18 @@
       <c r="B19" s="23">
         <v>5</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="42">
         <f>$B$15^A19*(1-$B$15)^(5-A19)</f>
         <v>0.0004303125</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="43">
         <f>B19*C19</f>
         <v>0.0021515625</v>
       </c>
       <c r="E19" s="23">
         <v>15</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="42">
         <f>D19*E19</f>
         <v>0.0322734375</v>
       </c>
@@ -11899,18 +11905,18 @@
       <c r="B20" s="23">
         <v>1</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="42">
         <f>$B$15^A20*(1-$B$15)^(5-A20)</f>
         <v>7.59375e-5</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="43">
         <f>B20*C20</f>
         <v>7.59375e-5</v>
       </c>
       <c r="E20" s="23">
         <v>20</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="42">
         <f>D20*E20</f>
         <v>0.00151875</v>
       </c>
@@ -11931,14 +11937,14 @@
       <c r="C21" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="45">
         <f>SUM(D18:D20)</f>
         <v>0.026611875</v>
       </c>
       <c r="E21" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="45">
         <f>SUM(F18:F20)</f>
         <v>0.2776359375</v>
       </c>
@@ -12155,23 +12161,23 @@
       <c r="A29" t="s">
         <v>140</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="42">
         <f>B27/B25</f>
         <v>0.15</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="42">
         <f>C27/C25</f>
         <v>0.15</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="42">
         <f>D27/D25</f>
         <v>0.15</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="42">
         <f>E27/E25</f>
         <v>0.15</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="42">
         <f>F27/F25</f>
         <v>0.157894736842105</v>
       </c>
@@ -12283,7 +12289,7 @@
         <f t="shared" ref="G33:G48" si="0">SUM(B33:F33)</f>
         <v>3</v>
       </c>
-      <c r="H33" s="8">
+      <c r="H33" s="42">
         <f t="shared" ref="H33:H48" si="1">IF(B33=1,$B$29,1-$B$29)*IF(C33=1,$C$29,1-$C$29)*IF(D33=1,$D$29,1-$D$29)*IF(E33=1,$E$29,1-$E$29)*IF(F33=1,$F$29,1-$F$29)</f>
         <v>0.00241578947368421</v>
       </c>
@@ -12311,7 +12317,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H34" s="8">
+      <c r="H34" s="42">
         <f t="shared" si="1"/>
         <v>0.00241578947368421</v>
       </c>
@@ -12339,7 +12345,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H35" s="8">
+      <c r="H35" s="42">
         <f t="shared" si="1"/>
         <v>0.00256677631578947</v>
       </c>
@@ -12367,7 +12373,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H36" s="8">
+      <c r="H36" s="42">
         <f t="shared" si="1"/>
         <v>0.00241578947368421</v>
       </c>
@@ -12395,7 +12401,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H37" s="8">
+      <c r="H37" s="42">
         <f t="shared" si="1"/>
         <v>0.00256677631578947</v>
       </c>
@@ -12423,7 +12429,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H38" s="8">
+      <c r="H38" s="42">
         <f t="shared" si="1"/>
         <v>0.00256677631578947</v>
       </c>
@@ -12451,7 +12457,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H39" s="8">
+      <c r="H39" s="42">
         <f t="shared" si="1"/>
         <v>0.00241578947368421</v>
       </c>
@@ -12479,7 +12485,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H40" s="8">
+      <c r="H40" s="42">
         <f t="shared" si="1"/>
         <v>0.00256677631578947</v>
       </c>
@@ -12507,7 +12513,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H41" s="8">
+      <c r="H41" s="42">
         <f t="shared" si="1"/>
         <v>0.00256677631578947</v>
       </c>
@@ -12535,7 +12541,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H42" s="8">
+      <c r="H42" s="42">
         <f t="shared" si="1"/>
         <v>0.00256677631578947</v>
       </c>
@@ -12563,7 +12569,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H43" s="8">
+      <c r="H43" s="42">
         <f t="shared" si="1"/>
         <v>0.000426315789473684</v>
       </c>
@@ -12591,7 +12597,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H44" s="8">
+      <c r="H44" s="42">
         <f t="shared" si="1"/>
         <v>0.000452960526315789</v>
       </c>
@@ -12619,7 +12625,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H45" s="8">
+      <c r="H45" s="42">
         <f t="shared" si="1"/>
         <v>0.000452960526315789</v>
       </c>
@@ -12647,7 +12653,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H46" s="8">
+      <c r="H46" s="42">
         <f t="shared" si="1"/>
         <v>0.000452960526315789</v>
       </c>
@@ -12675,7 +12681,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H47" s="8">
+      <c r="H47" s="42">
         <f t="shared" si="1"/>
         <v>0.000452960526315789</v>
       </c>
@@ -12703,7 +12709,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="H48" s="8">
+      <c r="H48" s="42">
         <f t="shared" si="1"/>
         <v>7.99342105263158e-5</v>
       </c>
@@ -12730,7 +12736,7 @@
       <c r="G49" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="H49" s="24">
+      <c r="H49" s="45">
         <f>SUM(H33:H48)</f>
         <v>0.0273819078947368</v>
       </c>
@@ -12794,7 +12800,7 @@
       <c r="B52" s="23">
         <v>10</v>
       </c>
-      <c r="C52" s="16">
+      <c r="C52" s="43">
         <f>SUMIF($G$33:$G$48,$A52,$H$33:$H$48)</f>
         <v>0.0250638157894737</v>
       </c>
@@ -12802,7 +12808,7 @@
         <f>E18</f>
         <v>10</v>
       </c>
-      <c r="E52" s="8">
+      <c r="E52" s="42">
         <f>C52*D52</f>
         <v>0.250638157894737</v>
       </c>
@@ -12823,7 +12829,7 @@
       <c r="B53" s="23">
         <v>5</v>
       </c>
-      <c r="C53" s="16">
+      <c r="C53" s="43">
         <f>SUMIF($G$33:$G$48,$A53,$H$33:$H$48)</f>
         <v>0.00223815789473684</v>
       </c>
@@ -12831,7 +12837,7 @@
         <f>E19</f>
         <v>15</v>
       </c>
-      <c r="E53" s="8">
+      <c r="E53" s="42">
         <f>C53*D53</f>
         <v>0.0335723684210526</v>
       </c>
@@ -12852,7 +12858,7 @@
       <c r="B54" s="23">
         <v>1</v>
       </c>
-      <c r="C54" s="16">
+      <c r="C54" s="43">
         <f>SUMIF($G$33:$G$48,$A54,$H$33:$H$48)</f>
         <v>7.99342105263158e-5</v>
       </c>
@@ -12860,7 +12866,7 @@
         <f>E20</f>
         <v>20</v>
       </c>
-      <c r="E54" s="8">
+      <c r="E54" s="42">
         <f>C54*D54</f>
         <v>0.00159868421052632</v>
       </c>
@@ -12881,14 +12887,14 @@
       <c r="B55" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C55" s="24">
+      <c r="C55" s="45">
         <f>SUM(C52:C54)</f>
         <v>0.0273819078947368</v>
       </c>
       <c r="D55" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="E55" s="16">
+      <c r="E55" s="43">
         <f>SUM(E52:E54)</f>
         <v>0.285809210526316</v>
       </c>
@@ -12961,7 +12967,7 @@
       <c r="B58" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C58" s="8">
+      <c r="C58" s="42">
         <f>滚轴与计数!$B$82*C55</f>
         <v>0.0547638157894737</v>
       </c>
@@ -13074,15 +13080,15 @@
       <c r="A5" t="s">
         <v>158</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="42">
         <f>Scatter与触发率!$D$18</f>
         <v>0.024384375</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="42">
         <f>Scatter与触发率!$D$19</f>
         <v>0.0021515625</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="42">
         <f>Scatter与触发率!$D$20</f>
         <v>7.59375e-5</v>
       </c>
@@ -13094,15 +13100,15 @@
       <c r="A6" t="s">
         <v>159</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="42">
         <f>Scatter与触发率!$C$52</f>
         <v>0.0250638157894737</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="42">
         <f>Scatter与触发率!$C$53</f>
         <v>0.00223815789473684</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="42">
         <f>Scatter与触发率!$C$54</f>
         <v>7.99342105263158e-5</v>
       </c>
@@ -13134,15 +13140,15 @@
       <c r="A8" t="s">
         <v>161</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="42">
         <f>B6*B7</f>
         <v>0.250638157894737</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="42">
         <f>C6*C7</f>
         <v>0.0335723684210526</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="42">
         <f>D6*D7</f>
         <v>0.00159868421052632</v>
       </c>
@@ -13171,7 +13177,7 @@
       <c r="A10" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="43">
         <f>SUM(B8:D8)</f>
         <v>0.285809210526316</v>
       </c>
@@ -13261,7 +13267,7 @@
       <c r="A15" t="s">
         <v>166</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="43">
         <f>单把RTP!$P$23</f>
         <v>1.02276546052632</v>
       </c>
@@ -13296,15 +13302,15 @@
       <c r="A17" t="s">
         <v>168</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="42">
         <f>B5*$B$15*B12</f>
         <v>0.349199358128103</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="42">
         <f>C5*$B$15*C12</f>
         <v>0.0462175621051901</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="42">
         <f>D5*$B$15*D12</f>
         <v>0.00217494409906777</v>
       </c>
@@ -13316,7 +13322,7 @@
       <c r="A18" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="43">
         <f>SUM(B17:D17)</f>
         <v>0.397591864332361</v>
       </c>
@@ -13368,7 +13374,7 @@
       <c r="A21" t="s">
         <v>172</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="42">
         <f>单把RTP!$P$12</f>
         <v>0.6500425</v>
       </c>
@@ -13386,7 +13392,7 @@
       <c r="A22" t="s">
         <v>173</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="42">
         <f>B18</f>
         <v>0.397591864332361</v>
       </c>
@@ -13404,7 +13410,7 @@
       <c r="A23" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="43">
         <f>B21+B22</f>
         <v>1.04763436433236</v>
       </c>
@@ -13559,7 +13565,7 @@
       <c r="A32" t="s">
         <v>182</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="42">
         <f>B23-B30</f>
         <v>4.33236113650537e-9</v>
       </c>
@@ -13718,7 +13724,7 @@
       <c r="A6" t="s">
         <v>188</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="41">
         <f>B5/B4</f>
         <v>0.285809210526316</v>
       </c>
@@ -13739,7 +13745,7 @@
       <c r="A7" t="s">
         <v>189</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="42">
         <f>免费游戏RTP!$B$18/免费游戏RTP!$B$11</f>
         <v>0.283956447475843</v>
       </c>
@@ -13828,7 +13834,7 @@
         <f>免费游戏RTP!B12</f>
         <v>14.0018607736028</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="42">
         <f>免费游戏RTP!$B$15</f>
         <v>1.02276546052632</v>
       </c>
@@ -13852,7 +13858,7 @@
         <f>免费游戏RTP!C12</f>
         <v>21.0027911604042</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="42">
         <f>免费游戏RTP!$B$15</f>
         <v>1.02276546052632</v>
       </c>
@@ -13876,7 +13882,7 @@
         <f>免费游戏RTP!D12</f>
         <v>28.0037215472056</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="42">
         <f>免费游戏RTP!$B$15</f>
         <v>1.02276546052632</v>
       </c>
@@ -13952,7 +13958,7 @@
       <c r="A17" s="14">
         <v>0</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="42">
         <f>A17*免费游戏RTP!$B$10</f>
         <v>0</v>
       </c>
@@ -13960,11 +13966,11 @@
         <f t="shared" ref="C17:C24" si="0">IF(B17&gt;=1,"发散",1/(1-B17))</f>
         <v>1</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="42">
         <f>IF(B17&gt;=1,"",(免费游戏RTP!$B$17+免费游戏RTP!$C$17+免费游戏RTP!$D$17)*(1/(1-B17))/免费游戏RTP!$B$11)</f>
         <v>0.283956447475843</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="42">
         <f>IF(B17&gt;=1,"",免费游戏RTP!$B$21+D17)</f>
         <v>0.933998947475843</v>
       </c>
@@ -13976,7 +13982,7 @@
       <c r="A18" s="14">
         <v>0.25</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="42">
         <f>A18*免费游戏RTP!$B$10</f>
         <v>0.071452302631579</v>
       </c>
@@ -13984,11 +13990,11 @@
         <f t="shared" si="0"/>
         <v>1.07695060020512</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="42">
         <f>IF(B18&gt;=1,"",(免费游戏RTP!$B$17+免费游戏RTP!$C$17+免费游戏RTP!$D$17)*(1/(1-B18))/免费游戏RTP!$B$11)</f>
         <v>0.305807066541222</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="42">
         <f>IF(B18&gt;=1,"",免费游戏RTP!$B$21+D18)</f>
         <v>0.955849566541222</v>
       </c>
@@ -14000,7 +14006,7 @@
       <c r="A19" s="14">
         <v>0.5</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="42">
         <f>A19*免费游戏RTP!$B$10</f>
         <v>0.142904605263158</v>
       </c>
@@ -14008,11 +14014,11 @@
         <f t="shared" si="0"/>
         <v>1.16673127185222</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="42">
         <f>IF(B19&gt;=1,"",(免费游戏RTP!$B$17+免费游戏RTP!$C$17+免费游戏RTP!$D$17)*(1/(1-B19))/免费游戏RTP!$B$11)</f>
         <v>0.331300867114129</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="42">
         <f>IF(B19&gt;=1,"",免费游戏RTP!$B$21+D19)</f>
         <v>0.981343367114129</v>
       </c>
@@ -14024,7 +14030,7 @@
       <c r="A20" s="14">
         <v>0.75</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="42">
         <f>A20*免费游戏RTP!$B$10</f>
         <v>0.214356907894737</v>
       </c>
@@ -14032,11 +14038,11 @@
         <f t="shared" si="0"/>
         <v>1.27284260505662</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="42">
         <f>IF(B20&gt;=1,"",(免费游戏RTP!$B$17+免费游戏RTP!$C$17+免费游戏RTP!$D$17)*(1/(1-B20))/免费游戏RTP!$B$11)</f>
         <v>0.361431864327775</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="42">
         <f>IF(B20&gt;=1,"",免费游戏RTP!$B$21+D20)</f>
         <v>1.01147436432777</v>
       </c>
@@ -14048,7 +14054,7 @@
       <c r="A21" s="14">
         <v>1</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="42">
         <f>A21*免费游戏RTP!$B$10</f>
         <v>0.285809210526316</v>
       </c>
@@ -14056,11 +14062,11 @@
         <f t="shared" si="0"/>
         <v>1.40018607736028</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="42">
         <f>IF(B21&gt;=1,"",(免费游戏RTP!$B$17+免费游戏RTP!$C$17+免费游戏RTP!$D$17)*(1/(1-B21))/免费游戏RTP!$B$11)</f>
         <v>0.397591864332361</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="42">
         <f>IF(B21&gt;=1,"",免费游戏RTP!$B$21+D21)</f>
         <v>1.04763436433236</v>
       </c>
@@ -14072,7 +14078,7 @@
       <c r="A22" s="14">
         <v>1.25</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="42">
         <f>A22*免费游戏RTP!$B$10</f>
         <v>0.357261513157895</v>
       </c>
@@ -14080,11 +14086,11 @@
         <f t="shared" si="0"/>
         <v>1.5558427268191</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="42">
         <f>IF(B22&gt;=1,"",(免费游戏RTP!$B$17+免费游戏RTP!$C$17+免费游戏RTP!$D$17)*(1/(1-B22))/免费游戏RTP!$B$11)</f>
         <v>0.441791573538679</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="42">
         <f>IF(B22&gt;=1,"",免费游戏RTP!$B$21+D22)</f>
         <v>1.09183407353868</v>
       </c>
@@ -14096,7 +14102,7 @@
       <c r="A23" s="14">
         <v>1.5</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="42">
         <f>A23*免费游戏RTP!$B$10</f>
         <v>0.428713815789474</v>
       </c>
@@ -14104,11 +14110,11 @@
         <f t="shared" si="0"/>
         <v>1.75043616953896</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="42">
         <f>IF(B23&gt;=1,"",(免费游戏RTP!$B$17+免费游戏RTP!$C$17+免费游戏RTP!$D$17)*(1/(1-B23))/免费游戏RTP!$B$11)</f>
         <v>0.497047636235504</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="42">
         <f>IF(B23&gt;=1,"",免费游戏RTP!$B$21+D23)</f>
         <v>1.1470901362355</v>
       </c>
@@ -14120,7 +14126,7 @@
       <c r="A24" s="14">
         <v>2</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="42">
         <f>A24*免费游戏RTP!$B$10</f>
         <v>0.571618421052632</v>
       </c>
@@ -14128,11 +14134,11 @@
         <f t="shared" si="0"/>
         <v>2.33436741714531</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="42">
         <f>IF(B24&gt;=1,"",(免费游戏RTP!$B$17+免费游戏RTP!$C$17+免费游戏RTP!$D$17)*(1/(1-B24))/免费游戏RTP!$B$11)</f>
         <v>0.662858678875943</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="42">
         <f>IF(B24&gt;=1,"",免费游戏RTP!$B$21+D24)</f>
         <v>1.31290117887594</v>
       </c>
